--- a/docs/design/Tetris_CLI_要件一覧.xlsx
+++ b/docs/design/Tetris_CLI_要件一覧.xlsx
@@ -21,11 +21,11 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'受け入れ基準(AC)'!$1:$2</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'受け入れ基準(AC)'!$A$2:$D$15</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">改訂履歴!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">改訂履歴!$A$2:$B$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">改訂履歴!$A$2:$B$13</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'機能要件(FR)'!$1:$2</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'機能要件(FR)'!$A$2:$E$18</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'非機能要件(NFR)'!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'非機能要件(NFR)'!$A$2:$E$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'非機能要件(NFR)'!$A$2:$E$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="207">
   <si>
     <r>
       <rPr>
@@ -57,6 +57,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">要件一覧・トレーサビリティ表</t>
     </r>
@@ -78,6 +79,7 @@
         <color rgb="FF4B5563"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（仕様駆動開発マスタードキュメント）に基づく要件・受け入れ基準・実装対応表</t>
     </r>
@@ -92,6 +94,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・本書は </t>
     </r>
@@ -111,6 +114,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に記載された機能要件</t>
     </r>
@@ -130,6 +134,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・非機能要件</t>
     </r>
@@ -149,6 +154,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・受け入れ基準</t>
     </r>
@@ -168,6 +174,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を、初見の人にも一覧できる表形式にまとめたものです。</t>
     </r>
@@ -179,6 +186,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・「設計書</t>
     </r>
@@ -198,6 +206,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">」が説明・アーキテクチャ・処理フローを解説するのに対し、本書は要件の一意な</t>
     </r>
@@ -217,6 +226,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・内容・相互の対応関係・実装</t>
     </r>
@@ -236,6 +246,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テストとの対応を管理する目的のシートです。</t>
     </r>
@@ -247,6 +258,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -266,6 +278,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">と </t>
     </r>
@@ -285,6 +298,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の対応関係、および各要件と実装モジュール</t>
     </r>
@@ -304,6 +318,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テストファイルとの対応は、</t>
     </r>
@@ -323,6 +338,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の記述をもとに本書作成時に整理したものであり、</t>
     </r>
@@ -342,6 +358,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">本文に表として明記されているものではありません。実装の詳細な対応は </t>
     </r>
@@ -361,6 +378,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">配下の各テストファイルを正としてください。</t>
     </r>
@@ -372,6 +390,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -391,6 +410,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -410,6 +430,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章での記載順</t>
     </r>
@@ -429,6 +450,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のみ経緯により章末に記載</t>
     </r>
@@ -448,6 +470,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を、本書では</t>
     </r>
@@ -467,6 +490,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">順</t>
     </r>
@@ -486,6 +510,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -497,7 +522,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11)</t>
+      <t xml:space="preserve">13)</t>
     </r>
     <r>
       <rPr>
@@ -505,6 +530,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に並べ替えています。</t>
     </r>
@@ -520,6 +546,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件</t>
     </r>
@@ -552,6 +579,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -571,6 +599,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・関連</t>
     </r>
@@ -590,6 +619,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・主な実装モジュール</t>
     </r>
@@ -602,6 +632,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件</t>
     </r>
@@ -634,6 +665,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -645,7 +677,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">NFR-11</t>
+      <t xml:space="preserve">NFR-13</t>
     </r>
     <r>
       <rPr>
@@ -653,6 +685,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・関連</t>
     </r>
@@ -672,6 +705,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・主な実装モジュール</t>
     </r>
@@ -684,6 +718,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準</t>
     </r>
@@ -716,6 +751,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -735,6 +771,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・対応テストファイル・関連</t>
     </r>
@@ -759,6 +796,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ソースモジュール一覧・役割・</t>
     </r>
@@ -778,6 +816,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依存の有無・対応テスト</t>
     </r>
@@ -802,6 +841,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章の改訂履歴（日付・内容）</t>
     </r>
@@ -816,6 +856,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件</t>
     </r>
@@ -835,6 +876,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -846,6 +888,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件</t>
     </r>
@@ -865,6 +908,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -876,6 +920,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準</t>
     </r>
@@ -895,6 +940,7 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -910,6 +956,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">※ テスト合格件数</t>
     </r>
@@ -931,6 +978,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件</t>
     </r>
@@ -952,6 +1000,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・壁打ちログ件数</t>
     </r>
@@ -964,7 +1013,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(6</t>
+      <t xml:space="preserve">(8</t>
     </r>
     <r>
       <rPr>
@@ -973,6 +1022,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件</t>
     </r>
@@ -994,6 +1044,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -1015,6 +1066,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行結果 </t>
     </r>
@@ -1036,6 +1088,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行</t>
     </r>
@@ -1057,6 +1110,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">及び </t>
     </r>
@@ -1078,6 +1132,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">配下のファイル数に基づく数値であり、本ブック内の表からは自動集計していません。</t>
     </r>
@@ -1090,6 +1145,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件 </t>
     </r>
@@ -1111,6 +1167,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -1129,6 +1186,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">関連する受け入れ基準</t>
     </r>
@@ -1160,6 +1218,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面は幅</t>
     </r>
@@ -1179,6 +1238,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス、高さ</t>
     </r>
@@ -1198,6 +1258,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マスとする。</t>
     </r>
@@ -1218,6 +1279,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テトリミノは </t>
     </r>
@@ -1237,6 +1299,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の</t>
     </r>
@@ -1256,6 +1319,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">種とし、</t>
     </r>
@@ -1275,6 +1339,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">方式で出現順を決定する。</t>
     </r>
@@ -1295,6 +1360,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">プレイヤーはミノの左右移動、時計回り</t>
     </r>
@@ -1314,6 +1380,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">反時計回り回転、ソフトドロップ、ハードドロップを行える。</t>
     </r>
@@ -1343,6 +1410,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回転により壁際で衝突する場合、簡易ウォールキック（左右</t>
     </r>
@@ -1362,6 +1430,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、</t>
     </r>
@@ -1381,6 +1450,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マスのオフセットを試す）を行い、それでも不可なら回転しない。</t>
     </r>
@@ -1405,6 +1475,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">簡易版（</t>
     </r>
@@ -1424,6 +1495,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章：完全準拠は将来拡張候補）</t>
     </r>
@@ -1438,6 +1510,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">横一列が完全に埋まった行はすべて消去し、上のブロックを詰める。</t>
     </r>
@@ -1457,6 +1530,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回の固定で同時に</t>
     </r>
@@ -1476,6 +1550,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -1495,6 +1570,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行を消去できる。</t>
     </r>
@@ -1519,6 +1595,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により実消去のタイミングは変更（下記参照）</t>
     </r>
@@ -1533,6 +1610,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">スコアはライン消去数とレベルに応じて加算する。同時消去数が多いほど</t>
     </r>
@@ -1552,6 +1630,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行あたりの得点効率が上がる。</t>
     </r>
@@ -1576,6 +1655,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1595,6 +1675,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1614,6 +1695,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1633,6 +1715,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1657,6 +1740,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ハードドロップは落下したマス数に応じたボーナス点（</t>
     </r>
@@ -1676,6 +1760,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス</t>
     </r>
@@ -1695,6 +1780,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">点）、ソフトドロップは</t>
     </r>
@@ -1714,6 +1800,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス</t>
     </r>
@@ -1733,6 +1820,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">点を加算する。</t>
     </r>
@@ -1750,6 +1838,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">消去した累計ライン数が</t>
     </r>
@@ -1769,6 +1858,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の倍数に達するごとにレベルが</t>
     </r>
@@ -1788,6 +1878,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">上昇し、落下間隔（重力）が短くなる。</t>
     </r>
@@ -1805,6 +1896,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">次に出現するミノを常に</t>
     </r>
@@ -1824,6 +1916,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">つ先読みしてプレビュー表示する。</t>
     </r>
@@ -1869,6 +1962,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（関連）</t>
     </r>
@@ -1890,6 +1984,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の消去エフェクト中の一時停止とも関連</t>
     </r>
@@ -1920,6 +2015,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">層のみ。</t>
     </r>
@@ -1939,6 +2035,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の対象外（自動テスト対象外）</t>
     </r>
@@ -1953,6 +2050,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面に表示するブロックはテトリミノの種類ごとに色分けして表示する（</t>
     </r>
@@ -1972,6 +2070,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">シアン</t>
     </r>
@@ -1991,6 +2090,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">黄</t>
     </r>
@@ -2010,6 +2110,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マゼンタ</t>
     </r>
@@ -2029,6 +2130,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">緑</t>
     </r>
@@ -2048,6 +2150,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">赤</t>
     </r>
@@ -2067,6 +2170,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">青</t>
     </r>
@@ -2086,6 +2190,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">白）。</t>
     </r>
@@ -2110,6 +2215,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により輪郭表示から塗りつぶし表示へ発展</t>
     </r>
@@ -2124,6 +2230,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面のブロックは輪郭表示ではなく背景色で塗りつぶした「ソリッド表示」とし、枠線・サイドバータイトル・状態メッセージにアクセントカラーを付ける（</t>
     </r>
@@ -2143,6 +2250,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">追加）。</t>
     </r>
@@ -2154,6 +2262,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -2178,6 +2287,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">横一列が完成した際、即座に消去せず一定時間の視覚エフェクト（点滅）を表示してから消去する。表示中は新規ミノ出現・重力・プレイヤー操作を一時停止する（</t>
     </r>
@@ -2197,6 +2307,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">追加）。</t>
     </r>
@@ -2211,6 +2322,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -2233,6 +2345,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件 </t>
     </r>
@@ -2254,6 +2367,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -2268,6 +2382,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行に外部パッケージを必須としない（標準ライブラリの </t>
     </r>
@@ -2287,6 +2402,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のみ使用。</t>
     </r>
@@ -2306,6 +2422,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">環境でのみ </t>
     </r>
@@ -2325,6 +2442,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加依存として許可）。</t>
     </r>
@@ -2342,6 +2460,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">入力から画面反映までの体感遅延がないこと（</t>
     </r>
@@ -2361,6 +2480,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">フレーム以内の処理）。</t>
     </r>
@@ -2372,6 +2492,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">―（</t>
     </r>
@@ -2391,6 +2512,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">と関連）</t>
     </r>
@@ -2408,6 +2530,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ロジック層（</t>
     </r>
@@ -2427,6 +2550,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）は </t>
     </r>
@@ -2446,6 +2570,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に非依存とし、</t>
     </r>
@@ -2465,6 +2590,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により自動テスト可能な設計とする。</t>
     </r>
@@ -2476,6 +2602,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">―（設計方針・全</t>
     </r>
@@ -2495,6 +2622,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の前提）</t>
     </r>
@@ -2522,6 +2650,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">以上で動作すること。</t>
     </r>
@@ -2546,6 +2675,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が画面へ描画する文字列は日本語で表示する。全角文字幅は </t>
     </r>
@@ -2565,6 +2695,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で判定し、確定した桁位置へ</t>
     </r>
@@ -2584,6 +2715,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">文字ずつ描画する。</t>
     </r>
@@ -2605,6 +2737,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">表示崩れの修正で明文化</t>
     </r>
@@ -2629,6 +2762,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を実行するたびに、成功・失敗にかかわらず実行結果を </t>
     </r>
@@ -2648,6 +2782,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ</t>
     </r>
@@ -2667,6 +2802,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイルとして記録する（ログ名は実行日時を含む一意な名前）。</t>
     </r>
@@ -2697,6 +2833,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の </t>
     </r>
@@ -2716,6 +2853,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・方針を追加</t>
     </r>
@@ -2735,6 +2873,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更</t>
     </r>
@@ -2754,6 +2893,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">削除する際は、変更に先立って壁打ちの要旨を </t>
     </r>
@@ -2773,6 +2913,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ記録する。</t>
     </r>
@@ -2792,6 +2933,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テーマ</t>
     </r>
@@ -2811,6 +2953,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイル、命名は </t>
     </r>
@@ -2830,6 +2973,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。</t>
     </r>
@@ -2847,6 +2991,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">詳細運用は </t>
     </r>
@@ -2866,6 +3011,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、雛形は </t>
     </r>
@@ -2890,6 +3036,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームループは「入力処理→固定タイムステップ更新→描画→フレームレート制御」の順に分離する。更新は固定タイムステップ</t>
     </r>
@@ -2909,6 +3056,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">アキュムレータ方式とし、経過時間の蓄積に上限を設けてスパイラル・オブ・デスを防ぐ。</t>
     </r>
@@ -2939,6 +3087,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の色分け表示は </t>
     </r>
@@ -2958,6 +3107,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が </t>
     </r>
@@ -2977,6 +3127,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の端末では色初期化をスキップし、モノクロ描画にフォールバックする。</t>
     </r>
@@ -3001,6 +3152,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の塗りつぶし表示・配色は、色非対応端末では従来通り輪郭表示・無配色にフォールバックする。標準</t>
     </r>
@@ -3020,6 +3172,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">色は</t>
     </r>
@@ -3039,6 +3192,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ミノ色で使い切っているため空セルには新色を割り当てない。</t>
     </r>
@@ -3063,6 +3217,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のエフェクトの時間管理は </t>
     </r>
@@ -3082,6 +3237,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に非依存なロジックとして </t>
     </r>
@@ -3101,6 +3257,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に実装し、</t>
     </r>
@@ -3120,6 +3277,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で単体テスト可能にする。点滅表現には </t>
     </r>
@@ -3139,8 +3297,389 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を用いる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPEC.md </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR/NFR/AC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を追加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">変更</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">削除する際は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の壁打ちログ運用に加えて、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/design/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">配下の説明資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">概要資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pptx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・設計書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・要件一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">xlsx)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">についても当該変更を反映するよう作成・更新する。個別の生成・更新手順は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cowork</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">上のスキル「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">design-doc-sync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">」を参照する。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/design/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-design-doc-sync.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tests/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">にテストを新規作成・変更した場合、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pytest </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">によるテスト合格確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(NFR-6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の後に、評価者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.claude/agents/reviewer.md)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">によるテスト観点レビューを、実装を行った作業セッションとは別のセッションで実行する。誤字修正等の軽微な変更には適用しない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">.claude/agents/reviewer.md</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-reviewer-separate-session.md</t>
     </r>
   </si>
   <si>
@@ -3151,6 +3690,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準 </t>
     </r>
@@ -3172,6 +3712,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -3187,6 +3728,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">関連</t>
     </r>
@@ -3239,6 +3781,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">同時に</t>
     </r>
@@ -3258,6 +3801,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行（テトリス）を消去した場合、</t>
     </r>
@@ -3277,6 +3821,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行消去より</t>
     </r>
@@ -3296,6 +3841,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行あたりの得点効率が高い。</t>
     </r>
@@ -3307,6 +3853,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">累計消去ライン数が</t>
     </r>
@@ -3326,6 +3873,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に達するとレベルが</t>
     </r>
@@ -3345,6 +3893,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">になり、レベルに応じて重力（落下間隔）が短くなる。</t>
     </r>
@@ -3356,6 +3905,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">新規ミノの出現位置に既にブロックがある場合、</t>
     </r>
@@ -3375,6 +3925,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が </t>
     </r>
@@ -3394,6 +3945,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">になる。</t>
     </r>
@@ -3424,6 +3976,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">方式では、連続する</t>
     </r>
@@ -3443,6 +3996,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回のミノ出現に同じ種類の重複がない。</t>
     </r>
@@ -3469,6 +4023,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">極端に大きな経過時間が与えられても、アキュムレータは上限（</t>
     </r>
@@ -3488,6 +4043,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）でクランプされ、無限に更新し続けない。</t>
     </r>
@@ -3508,6 +4064,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">一列以上が完成すると </t>
     </r>
@@ -3527,6 +4084,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に対象行が設定され即座には消去されない。</t>
     </r>
@@ -3546,6 +4104,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を呼び続けると一定時間後に消去・次ミノ出現する。表示中は重力・操作が反映されない。</t>
     </r>
@@ -3564,6 +4123,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">モジュール構成 — </t>
     </r>
@@ -3585,6 +4145,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -3614,6 +4175,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依存</t>
     </r>
@@ -3640,6 +4202,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テトリミノ形状・回転定義（</t>
     </r>
@@ -3659,6 +4222,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">簡易版）、</t>
     </r>
@@ -3678,6 +4242,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">抽選</t>
     </r>
@@ -3695,6 +4260,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面状態・衝突判定・ライン消去（判定</t>
     </r>
@@ -3714,6 +4280,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実消去の分離を含む）</t>
     </r>
@@ -3731,6 +4298,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームロジック本体・スコア</t>
     </r>
@@ -3750,6 +4318,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">レベル管理・ライン消去エフェクトの時間管理</t>
     </r>
@@ -3767,6 +4336,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">固定タイムステップ制御（</t>
     </r>
@@ -3786,6 +4356,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）・フレームレート制御（</t>
     </r>
@@ -3805,6 +4376,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）</t>
     </r>
@@ -3829,6 +4401,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">描画・キー入力。盤面</t>
     </r>
@@ -3848,6 +4421,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">サイドバー描画、配色、点滅エフェクト表示</t>
     </r>
@@ -3875,6 +4449,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行ログを </t>
     </r>
@@ -3894,6 +4469,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ出力する仕組み（</t>
     </r>
@@ -3913,6 +4489,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）</t>
     </r>
@@ -3928,6 +4505,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">設計方針（</t>
     </r>
@@ -3949,6 +4527,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章）</t>
     </r>
@@ -3970,6 +4549,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">以下のロジック層は </t>
     </r>
@@ -3991,6 +4571,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を一切</t>
     </r>
@@ -4012,6 +4593,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">しない。</t>
     </r>
@@ -4033,6 +4615,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -4054,6 +4637,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に閉じ込め、</t>
     </r>
@@ -4075,6 +4659,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の公開メソッドを呼び出すだけにすることで、</t>
     </r>
@@ -4096,6 +4681,7 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">からロジックのみを直接テストできるようにしている。</t>
     </r>
@@ -4108,6 +4694,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">改訂履歴 — </t>
     </r>
@@ -4129,6 +4716,7 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -4146,6 +4734,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">初版作成。</t>
     </r>
@@ -4165,6 +4754,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4184,6 +4774,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4203,6 +4794,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4222,6 +4814,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を定義。</t>
     </r>
@@ -4243,6 +4836,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -4262,6 +4856,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">環境で</t>
     </r>
@@ -4281,6 +4876,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">操作ヘルプ等の全角文字がずれて重なって表示される不具合が発見されたため、</t>
     </r>
@@ -4300,6 +4896,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">描画文字列を</t>
     </r>
@@ -4319,6 +4916,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">限定とする方針を明文化し、</t>
     </r>
@@ -4338,6 +4936,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を修正。</t>
     </r>
@@ -4359,6 +4958,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -4378,6 +4978,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行のたびに </t>
     </r>
@@ -4397,6 +4998,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ</t>
     </r>
@@ -4416,6 +5018,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイルの実行ログを残す要件を明文化し、</t>
     </r>
@@ -4435,6 +5038,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加して実装。</t>
     </r>
@@ -4456,6 +5060,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -4475,6 +5080,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -4494,6 +5100,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。ゲームループを「入力→固定タイムステップ更新→描画→フレームレート制御」に明確に分離するため、</t>
     </r>
@@ -4513,6 +5120,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（</t>
     </r>
@@ -4532,6 +5140,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）を新規実装し、</t>
     </r>
@@ -4551,6 +5160,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の </t>
     </r>
@@ -4570,6 +5180,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を書き換えた。壁打ちログ</t>
     </r>
@@ -4604,6 +5215,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -4623,6 +5235,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。盤面のブロック（落下中ピース・固定ブロック）をミノの種類ごとに色分け表示するようにした。色非対応端末ではモノクロにフォールバックする。壁打ちログ</t>
     </r>
@@ -4654,6 +5267,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -4673,6 +5287,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更時に設計判断の壁打ち要旨を </t>
     </r>
@@ -4692,6 +5307,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ残す運用を明文化。</t>
     </r>
@@ -4711,6 +5327,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、</t>
     </r>
@@ -4730,6 +5347,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（</t>
     </r>
@@ -4749,6 +5367,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）を新設。壁打ちログ</t>
     </r>
@@ -4780,6 +5399,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を改訂。</t>
     </r>
@@ -4799,6 +5419,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">画面の表示文字列を </t>
     </r>
@@ -4818,6 +5439,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">限定から日本語表示へ変更。</t>
     </r>
@@ -4837,6 +5459,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の全角文字重なり不具合は、表示幅を </t>
     </r>
@@ -4856,6 +5479,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で明示計算して</t>
     </r>
@@ -4875,6 +5499,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">文字ずつ描画する方式で回避する。</t>
     </r>
@@ -4894,6 +5519,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に </t>
     </r>
@@ -4913,6 +5539,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加して実装。壁打ちログ</t>
     </r>
@@ -4944,6 +5571,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -4963,6 +5591,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -4982,6 +5611,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。盤面のブロックを輪郭表示から塗りつぶし表示に変更し、盤面の枠線・サイドバーのタイトル・一時停止</t>
     </r>
@@ -5001,6 +5631,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームオーバーの状態メッセージに標準</t>
     </r>
@@ -5020,6 +5651,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">色でアクセントカラーを付けた（配色・見た目のモダン化）。色非対応端末では従来通りの無配色表示にフォールバックする。壁打ちログ</t>
     </r>
@@ -5051,6 +5683,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5070,6 +5703,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5089,6 +5723,7 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。横一列が完成してから実際に盤面から消去されるまでの間、対象行を一定時間・点滅（反転表示）させるライン消去エフェクトを追加した。エフェクト表示中は重力・新規ミノ出現・プレイヤー操作を一時停止する。壁打ちログ</t>
     </r>
@@ -5101,6 +5736,250 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: docs/spec-log/2026-09-12-line-clear-effect.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を追加。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPEC.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR/NFR/AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">変更時に、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/design/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">配下の説明資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">概要資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pptx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・設計書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・要件一覧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">xlsx)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">も更新することを明文化した。壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-design-doc-sync.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を追加。テストを新規作成・変更した場合、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">合格確認の後に、評価者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.claude/agents/reviewer.md)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">によるテスト観点レビューを別セッションで実行することを明文化した。壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-reviewer-separate-session.md</t>
     </r>
   </si>
 </sst>
@@ -5149,6 +6028,7 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5162,6 +6042,7 @@
       <color rgb="FF4B5563"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5169,12 +6050,14 @@
       <color rgb="FF3B6EA5"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -5189,6 +6072,7 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5212,6 +6096,7 @@
       <color rgb="FF6B7280"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -5227,6 +6112,7 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5250,12 +6136,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -5334,96 +6222,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5751,143 +6643,143 @@
   <dimension ref="B2:C24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <f aca="false">COUNTA('機能要件(FR)'!A3:A100)</f>
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="9" t="n">
         <f aca="false">COUNTA('非機能要件(NFR)'!A3:A100)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <f aca="false">COUNTA('受け入れ基準(AC)'!A3:A100)</f>
         <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="9" t="n">
         <f aca="false">COUNTA(モジュール構成!A3:A9)</f>
         <v>7</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5917,293 +6809,293 @@
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+    <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+    <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="18" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6228,216 +7120,250 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+    <row r="3" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+    <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>89</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E13"/>
+  <autoFilter ref="A2:E15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -6460,214 +7386,214 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="C2" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="B4" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="D6" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="B7" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="B8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="B9" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="B10" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="B11" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" s="18" t="s">
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" s="15" t="s">
+    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+    <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="B14" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>157</v>
+      <c r="B15" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6694,139 +7620,139 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>162</v>
+      <c r="A2" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="A3" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>146</v>
+      <c r="A4" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>171</v>
+      <c r="A5" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>174</v>
+      <c r="A6" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>149</v>
+      <c r="D7" s="16" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>180</v>
+      <c r="A8" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>182</v>
+      <c r="B9" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="A11" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:D9"/>
@@ -6850,101 +7776,117 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="108"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="108"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>187</v>
+      <c r="A3" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>188</v>
+      <c r="A4" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>189</v>
+      <c r="A5" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>190</v>
+      <c r="A6" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>192</v>
+      <c r="A7" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>193</v>
+      <c r="A8" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="22" t="s">
         <v>194</v>
       </c>
+      <c r="B9" s="16" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>195</v>
+      <c r="A10" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>196</v>
+      <c r="A11" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B11"/>
+  <autoFilter ref="A2:B13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>

--- a/docs/design/Tetris_CLI_要件一覧.xlsx
+++ b/docs/design/Tetris_CLI_要件一覧.xlsx
@@ -17,15 +17,15 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">モジュール構成!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">モジュール構成!$A$2:$D$9</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">モジュール構成!$A$2:$D$10</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'受け入れ基準(AC)'!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'受け入れ基準(AC)'!$A$2:$D$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'受け入れ基準(AC)'!$A$2:$D$21</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">改訂履歴!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">改訂履歴!$A$2:$B$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">改訂履歴!$A$2:$B$14</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'機能要件(FR)'!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'機能要件(FR)'!$A$2:$E$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'機能要件(FR)'!$A$2:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'非機能要件(NFR)'!$1:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'非機能要件(NFR)'!$A$2:$E$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'非機能要件(NFR)'!$A$2:$E$18</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="252">
   <si>
     <r>
       <rPr>
@@ -57,7 +57,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">要件一覧・トレーサビリティ表</t>
     </r>
@@ -79,7 +78,6 @@
         <color rgb="FF4B5563"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（仕様駆動開発マスタードキュメント）に基づく要件・受け入れ基準・実装対応表</t>
     </r>
@@ -94,7 +92,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・本書は </t>
     </r>
@@ -114,7 +111,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に記載された機能要件</t>
     </r>
@@ -134,7 +130,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・非機能要件</t>
     </r>
@@ -154,7 +149,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・受け入れ基準</t>
     </r>
@@ -174,7 +168,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を、初見の人にも一覧できる表形式にまとめたものです。</t>
     </r>
@@ -186,7 +179,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・「設計書</t>
     </r>
@@ -206,7 +198,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">」が説明・アーキテクチャ・処理フローを解説するのに対し、本書は要件の一意な</t>
     </r>
@@ -226,7 +217,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・内容・相互の対応関係・実装</t>
     </r>
@@ -246,7 +236,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テストとの対応を管理する目的のシートです。</t>
     </r>
@@ -258,7 +247,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -278,7 +266,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">と </t>
     </r>
@@ -298,7 +285,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の対応関係、および各要件と実装モジュール</t>
     </r>
@@ -318,7 +304,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テストファイルとの対応は、</t>
     </r>
@@ -338,7 +323,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の記述をもとに本書作成時に整理したものであり、</t>
     </r>
@@ -358,7 +342,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">本文に表として明記されているものではありません。実装の詳細な対応は </t>
     </r>
@@ -378,7 +361,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">配下の各テストファイルを正としてください。</t>
     </r>
@@ -390,7 +372,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -410,7 +391,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -430,7 +410,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章での記載順</t>
     </r>
@@ -450,7 +429,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のみ経緯により章末に記載</t>
     </r>
@@ -470,7 +448,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を、本書では</t>
     </r>
@@ -490,7 +467,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">順</t>
     </r>
@@ -510,7 +486,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -522,7 +497,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13)</t>
+      <t xml:space="preserve">16)</t>
     </r>
     <r>
       <rPr>
@@ -530,7 +505,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に並べ替えています。</t>
     </r>
@@ -546,7 +520,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件</t>
     </r>
@@ -579,7 +552,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -591,7 +563,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FR-16</t>
+      <t xml:space="preserve">FR-22</t>
     </r>
     <r>
       <rPr>
@@ -599,7 +571,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・関連</t>
     </r>
@@ -619,7 +590,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・主な実装モジュール</t>
     </r>
@@ -632,7 +602,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件</t>
     </r>
@@ -665,7 +634,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -677,7 +645,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">NFR-13</t>
+      <t xml:space="preserve">NFR-16</t>
     </r>
     <r>
       <rPr>
@@ -685,7 +653,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・関連</t>
     </r>
@@ -705,7 +672,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・主な実装モジュール</t>
     </r>
@@ -718,7 +684,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準</t>
     </r>
@@ -751,7 +716,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -763,7 +727,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AC-13</t>
+      <t xml:space="preserve">AC-19</t>
     </r>
     <r>
       <rPr>
@@ -771,7 +735,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。内容・対応テストファイル・関連</t>
     </r>
@@ -796,7 +759,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ソースモジュール一覧・役割・</t>
     </r>
@@ -816,7 +778,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依存の有無・対応テスト</t>
     </r>
@@ -841,7 +802,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章の改訂履歴（日付・内容）</t>
     </r>
@@ -856,7 +816,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件</t>
     </r>
@@ -876,7 +835,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -888,7 +846,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件</t>
     </r>
@@ -908,7 +865,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -920,7 +876,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準</t>
     </r>
@@ -940,7 +895,6 @@
         <color rgb="FF333333"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件数</t>
     </r>
@@ -956,7 +910,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">※ テスト合格件数</t>
     </r>
@@ -969,7 +922,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(56</t>
+      <t xml:space="preserve">(67</t>
     </r>
     <r>
       <rPr>
@@ -978,7 +931,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件</t>
     </r>
@@ -1000,7 +952,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・壁打ちログ件数</t>
     </r>
@@ -1013,7 +964,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(8</t>
+      <t xml:space="preserve">(9</t>
     </r>
     <r>
       <rPr>
@@ -1022,7 +973,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">件</t>
     </r>
@@ -1044,7 +994,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -1057,7 +1006,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">pytest </t>
+      <t xml:space="preserve">docs/spec-log/ </t>
     </r>
     <r>
       <rPr>
@@ -1066,9 +1015,8 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">実行結果 </t>
+      </rPr>
+      <t xml:space="preserve">配下のファイル数、及び </t>
     </r>
     <r>
       <rPr>
@@ -1079,7 +1027,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(logs/test_run_20260912T030737*.log, 2026-09-12</t>
+      <t xml:space="preserve">tests/ </t>
     </r>
     <r>
       <rPr>
@@ -1088,9 +1036,8 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">実行</t>
+      </rPr>
+      <t xml:space="preserve">配下のテスト実行結果に基づく数値であり、本ブック内の表からは自動集計していません。</t>
     </r>
     <r>
       <rPr>
@@ -1101,7 +1048,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">2026-09-12</t>
     </r>
     <r>
       <rPr>
@@ -1110,9 +1057,8 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">及び </t>
+      </rPr>
+      <t xml:space="preserve">の</t>
     </r>
     <r>
       <rPr>
@@ -1123,7 +1069,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">docs/spec-log/ </t>
+      <t xml:space="preserve">FR-17</t>
     </r>
     <r>
       <rPr>
@@ -1132,9 +1078,155 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">配下のファイル数に基づく数値であり、本ブック内の表からは自動集計していません。</t>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等追加分については開発環境で</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が利用できなかったため、</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">互換の簡易テストランナーで</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件全件の成功を確認しています</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(logs/</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">への正式なログ記録</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(NFR-6)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は未実施</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
   </si>
   <si>
@@ -1145,7 +1237,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">機能要件 </t>
     </r>
@@ -1167,7 +1258,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -1186,7 +1276,6 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">関連する受け入れ基準</t>
     </r>
@@ -1218,7 +1307,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面は幅</t>
     </r>
@@ -1238,7 +1326,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス、高さ</t>
     </r>
@@ -1258,7 +1345,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マスとする。</t>
     </r>
@@ -1279,7 +1365,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テトリミノは </t>
     </r>
@@ -1299,7 +1384,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の</t>
     </r>
@@ -1319,7 +1403,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">種とし、</t>
     </r>
@@ -1339,7 +1422,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">方式で出現順を決定する。</t>
     </r>
@@ -1360,7 +1442,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">プレイヤーはミノの左右移動、時計回り</t>
     </r>
@@ -1380,7 +1461,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">反時計回り回転、ソフトドロップ、ハードドロップを行える。</t>
     </r>
@@ -1410,7 +1490,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回転により壁際で衝突する場合、簡易ウォールキック（左右</t>
     </r>
@@ -1430,7 +1509,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、</t>
     </r>
@@ -1450,7 +1528,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マスのオフセットを試す）を行い、それでも不可なら回転しない。</t>
     </r>
@@ -1475,7 +1552,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">簡易版（</t>
     </r>
@@ -1495,7 +1571,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章：完全準拠は将来拡張候補）</t>
     </r>
@@ -1510,7 +1585,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">横一列が完全に埋まった行はすべて消去し、上のブロックを詰める。</t>
     </r>
@@ -1530,7 +1604,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回の固定で同時に</t>
     </r>
@@ -1550,7 +1623,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -1570,7 +1642,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行を消去できる。</t>
     </r>
@@ -1595,7 +1666,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により実消去のタイミングは変更（下記参照）</t>
     </r>
@@ -1610,7 +1680,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">スコアはライン消去数とレベルに応じて加算する。同時消去数が多いほど</t>
     </r>
@@ -1630,7 +1699,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行あたりの得点効率が上がる。</t>
     </r>
@@ -1655,7 +1723,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1675,7 +1742,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1695,7 +1761,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1715,7 +1780,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行</t>
     </r>
@@ -1740,7 +1804,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ハードドロップは落下したマス数に応じたボーナス点（</t>
     </r>
@@ -1760,7 +1823,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス</t>
     </r>
@@ -1780,7 +1842,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">点）、ソフトドロップは</t>
     </r>
@@ -1800,7 +1861,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マス</t>
     </r>
@@ -1820,7 +1880,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">点を加算する。</t>
     </r>
@@ -1838,7 +1897,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">消去した累計ライン数が</t>
     </r>
@@ -1858,7 +1916,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の倍数に達するごとにレベルが</t>
     </r>
@@ -1878,7 +1935,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">上昇し、落下間隔（重力）が短くなる。</t>
     </r>
@@ -1896,7 +1952,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">次に出現するミノを常に</t>
     </r>
@@ -1916,7 +1971,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">つ先読みしてプレビュー表示する。</t>
     </r>
@@ -1962,7 +2016,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（関連）</t>
     </r>
@@ -1984,7 +2037,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の消去エフェクト中の一時停止とも関連</t>
     </r>
@@ -2015,7 +2067,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">層のみ。</t>
     </r>
@@ -2035,7 +2086,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の対象外（自動テスト対象外）</t>
     </r>
@@ -2050,7 +2100,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面に表示するブロックはテトリミノの種類ごとに色分けして表示する（</t>
     </r>
@@ -2070,7 +2119,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">シアン</t>
     </r>
@@ -2090,7 +2138,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">黄</t>
     </r>
@@ -2110,7 +2157,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マゼンタ</t>
     </r>
@@ -2130,7 +2176,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">緑</t>
     </r>
@@ -2150,7 +2195,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">赤</t>
     </r>
@@ -2170,7 +2214,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">青</t>
     </r>
@@ -2190,7 +2233,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">白）。</t>
     </r>
@@ -2215,7 +2257,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により輪郭表示から塗りつぶし表示へ発展</t>
     </r>
@@ -2230,7 +2271,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面のブロックは輪郭表示ではなく背景色で塗りつぶした「ソリッド表示」とし、枠線・サイドバータイトル・状態メッセージにアクセントカラーを付ける（</t>
     </r>
@@ -2250,7 +2290,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">追加）。</t>
     </r>
@@ -2262,7 +2301,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -2287,7 +2325,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">横一列が完成した際、即座に消去せず一定時間の視覚エフェクト（点滅）を表示してから消去する。表示中は新規ミノ出現・重力・プレイヤー操作を一時停止する（</t>
     </r>
@@ -2307,7 +2344,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">追加）。</t>
     </r>
@@ -2322,7 +2358,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -2336,6 +2371,527 @@
       </rPr>
       <t xml:space="preserve">: docs/spec-log/2026-09-12-line-clear-effect.md</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起動時にコマンドライン引数 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">--2p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を指定した場合は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードで起動する（未指定時は従来通り</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人用）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードでは同一端末・同一プロセス上で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの盤面を画面分割表示し、共有キーボードで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が操作できる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">main.py / ui_curses.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-two-player-battle-mode.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードでは、各プレイヤーが独立した盤面・ミノ出現・スコア・レベル・ライン消去数を持つ。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR-11, FR-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR-16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は各プレイヤーの盤面に個別適用</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同時に複数行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を消去した場合、消去行数に応じた非線形の「攻撃力」を算出し、相手へ「お邪魔行」として送る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1/2/3/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行消去→攻撃力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0/1/2/4)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">送信された攻撃力は即座に反映せず相手の「保留お邪魔行数」に加算し、相手の次のミノのロック時に、自分の消去による相殺→残りの盤面反映、の順で処理する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-17</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.py / game.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反映は次のミノ出現直前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライン消去エフェクト完了後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に行う</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-21</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">お邪魔行は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行につきランダムに選んだ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列を空け、それ以外のマスを固定ブロックで埋めた行とする。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードでは、いずれかのプレイヤーの盤面がゲームオーバーになった時点で対戦を終了し、もう一方の勝利とする。同一タイミングで両者ゲームオーバーの場合は引き分けとする。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-19</t>
   </si>
   <si>
     <r>
@@ -2345,7 +2901,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">非機能要件 </t>
     </r>
@@ -2367,7 +2922,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -2382,7 +2936,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行に外部パッケージを必須としない（標準ライブラリの </t>
     </r>
@@ -2402,7 +2955,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のみ使用。</t>
     </r>
@@ -2422,7 +2974,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">環境でのみ </t>
     </r>
@@ -2442,7 +2993,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加依存として許可）。</t>
     </r>
@@ -2460,7 +3010,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">入力から画面反映までの体感遅延がないこと（</t>
     </r>
@@ -2480,7 +3029,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">フレーム以内の処理）。</t>
     </r>
@@ -2492,7 +3040,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">―（</t>
     </r>
@@ -2512,7 +3059,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">と関連）</t>
     </r>
@@ -2530,7 +3076,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ロジック層（</t>
     </r>
@@ -2550,7 +3095,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）は </t>
     </r>
@@ -2570,7 +3114,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に非依存とし、</t>
     </r>
@@ -2590,7 +3133,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">により自動テスト可能な設計とする。</t>
     </r>
@@ -2602,7 +3144,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">―（設計方針・全</t>
     </r>
@@ -2622,7 +3163,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の前提）</t>
     </r>
@@ -2650,7 +3190,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">以上で動作すること。</t>
     </r>
@@ -2675,7 +3214,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が画面へ描画する文字列は日本語で表示する。全角文字幅は </t>
     </r>
@@ -2695,7 +3233,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で判定し、確定した桁位置へ</t>
     </r>
@@ -2715,7 +3252,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">文字ずつ描画する。</t>
     </r>
@@ -2737,7 +3273,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">表示崩れの修正で明文化</t>
     </r>
@@ -2762,7 +3297,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を実行するたびに、成功・失敗にかかわらず実行結果を </t>
     </r>
@@ -2782,7 +3316,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ</t>
     </r>
@@ -2802,7 +3335,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイルとして記録する（ログ名は実行日時を含む一意な名前）。</t>
     </r>
@@ -2833,7 +3365,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の </t>
     </r>
@@ -2853,7 +3384,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・方針を追加</t>
     </r>
@@ -2873,7 +3403,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更</t>
     </r>
@@ -2893,7 +3422,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">削除する際は、変更に先立って壁打ちの要旨を </t>
     </r>
@@ -2913,7 +3441,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ記録する。</t>
     </r>
@@ -2933,7 +3460,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テーマ</t>
     </r>
@@ -2953,7 +3479,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイル、命名は </t>
     </r>
@@ -2973,7 +3498,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">。</t>
     </r>
@@ -2991,7 +3515,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">詳細運用は </t>
     </r>
@@ -3011,7 +3534,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、雛形は </t>
     </r>
@@ -3036,7 +3558,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームループは「入力処理→固定タイムステップ更新→描画→フレームレート制御」の順に分離する。更新は固定タイムステップ</t>
     </r>
@@ -3056,7 +3577,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">アキュムレータ方式とし、経過時間の蓄積に上限を設けてスパイラル・オブ・デスを防ぐ。</t>
     </r>
@@ -3087,7 +3607,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の色分け表示は </t>
     </r>
@@ -3107,7 +3626,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が </t>
     </r>
@@ -3127,7 +3645,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の端末では色初期化をスキップし、モノクロ描画にフォールバックする。</t>
     </r>
@@ -3152,7 +3669,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の塗りつぶし表示・配色は、色非対応端末では従来通り輪郭表示・無配色にフォールバックする。標準</t>
     </r>
@@ -3172,7 +3688,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">色は</t>
     </r>
@@ -3192,7 +3707,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ミノ色で使い切っているため空セルには新色を割り当てない。</t>
     </r>
@@ -3217,7 +3731,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">のエフェクトの時間管理は </t>
     </r>
@@ -3237,7 +3750,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に非依存なロジックとして </t>
     </r>
@@ -3257,7 +3769,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に実装し、</t>
     </r>
@@ -3277,7 +3788,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で単体テスト可能にする。点滅表現には </t>
     </r>
@@ -3297,7 +3807,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を用いる。</t>
     </r>
@@ -3322,7 +3831,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の </t>
     </r>
@@ -3342,7 +3850,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加</t>
     </r>
@@ -3362,7 +3869,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更</t>
     </r>
@@ -3382,7 +3888,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">削除する際は、</t>
     </r>
@@ -3402,7 +3907,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の壁打ちログ運用に加えて、</t>
     </r>
@@ -3422,7 +3926,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">配下の説明資料</t>
     </r>
@@ -3442,7 +3945,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">概要資料</t>
     </r>
@@ -3462,7 +3964,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・設計書</t>
     </r>
@@ -3482,7 +3983,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・要件一覧</t>
     </r>
@@ -3502,7 +4002,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">についても当該変更を反映するよう作成・更新する。個別の生成・更新手順は</t>
     </r>
@@ -3522,7 +4021,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">上のスキル「</t>
     </r>
@@ -3542,7 +4040,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">」を参照する。</t>
     </r>
@@ -3557,7 +4054,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -3592,7 +4088,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">にテストを新規作成・変更した場合、</t>
     </r>
@@ -3612,7 +4107,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">によるテスト合格確認</t>
     </r>
@@ -3632,7 +4126,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の後に、評価者</t>
     </r>
@@ -3652,7 +4145,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">によるテスト観点レビューを、実装を行った作業セッションとは別のセッションで実行する。誤字修正等の軽微な変更には適用しない。</t>
     </r>
@@ -3667,7 +4159,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">壁打ちログ</t>
     </r>
@@ -3680,6 +4171,411 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: docs/spec-log/2026-09-12-reviewer-separate-session.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードのロジック</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">お邪魔行の攻撃力算出・保留キュー管理・相殺・盤面への反映・勝敗判定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">curses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に非依存な形で実装し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pytest </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で単体テスト可能にする。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-19</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の方針を踏襲</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードの盤面分割描画・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレイヤーを含むキー入力の振り分けは </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ui_curses.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に閉じ込め、ロジック層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(NFR-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の対象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に影響しない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">―（設計方針）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードにおける第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレイヤーのキー割り当ては、既存の第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレイヤーのキー割り当ておよび共通操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一時停止・終了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と重複しない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章参照。第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレイヤー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: A/D/S/W/E/F</t>
     </r>
   </si>
   <si>
@@ -3690,7 +4586,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受け入れ基準 </t>
     </r>
@@ -3712,7 +4607,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -3728,7 +4622,6 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">関連</t>
     </r>
@@ -3781,7 +4674,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">同時に</t>
     </r>
@@ -3801,7 +4693,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行（テトリス）を消去した場合、</t>
     </r>
@@ -3821,7 +4712,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行消去より</t>
     </r>
@@ -3841,7 +4731,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">行あたりの得点効率が高い。</t>
     </r>
@@ -3853,7 +4742,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">累計消去ライン数が</t>
     </r>
@@ -3873,7 +4761,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に達するとレベルが</t>
     </r>
@@ -3893,7 +4780,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">になり、レベルに応じて重力（落下間隔）が短くなる。</t>
     </r>
@@ -3905,7 +4791,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">新規ミノの出現位置に既にブロックがある場合、</t>
     </r>
@@ -3925,7 +4810,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">が </t>
     </r>
@@ -3945,7 +4829,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">になる。</t>
     </r>
@@ -3976,7 +4859,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">方式では、連続する</t>
     </r>
@@ -3996,7 +4878,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回のミノ出現に同じ種類の重複がない。</t>
     </r>
@@ -4023,7 +4904,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">極端に大きな経過時間が与えられても、アキュムレータは上限（</t>
     </r>
@@ -4043,7 +4923,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）でクランプされ、無限に更新し続けない。</t>
     </r>
@@ -4064,7 +4943,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">一列以上が完成すると </t>
     </r>
@@ -4084,7 +4962,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に対象行が設定され即座には消去されない。</t>
     </r>
@@ -4104,7 +4981,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を呼び続けると一定時間後に消去・次ミノ出現する。表示中は重力・操作が反映されない。</t>
     </r>
@@ -4114,6 +4990,447 @@
   </si>
   <si>
     <t xml:space="preserve">FR-16, NFR-11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行のライン消去に対し、算出される攻撃力がそれぞれ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0/1/2/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">であること。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/test_battle.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保留お邪魔行数が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のとき、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行消去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">攻撃力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">すると保留お邪魔行数は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に減り、相手への新規攻撃は発生しない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保留お邪魔行数が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のとき、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行消去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">攻撃力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">すると保留お邪魔行数は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">になり、相手へ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行分の攻撃が新たに送信される。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保留お邪魔行数がある状態で対象プレイヤーの次のミノがロックすると、相殺処理後に残った保留分がその時点で盤面に追加され、保留お邪魔行数が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にリセットされる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">追加されたお邪魔行は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行につきちょうど</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列が空いており、それ以外の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マスが固定ブロックで埋まっている。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">一方のプレイヤーの盤面がゲームオーバーになった時点で対戦全体が終了し、もう一方のプレイヤーが勝者と判定される。</t>
   </si>
   <si>
     <r>
@@ -4123,7 +5440,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">モジュール構成 — </t>
     </r>
@@ -4145,7 +5461,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -4175,7 +5490,6 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依存</t>
     </r>
@@ -4202,7 +5516,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">テトリミノ形状・回転定義（</t>
     </r>
@@ -4222,7 +5535,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">簡易版）、</t>
     </r>
@@ -4242,7 +5554,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">抽選</t>
     </r>
@@ -4260,7 +5571,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">盤面状態・衝突判定・ライン消去（判定</t>
     </r>
@@ -4280,7 +5590,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実消去の分離を含む）</t>
     </r>
@@ -4298,7 +5607,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームロジック本体・スコア</t>
     </r>
@@ -4318,7 +5626,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">レベル管理・ライン消去エフェクトの時間管理</t>
     </r>
@@ -4336,7 +5643,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">固定タイムステップ制御（</t>
     </r>
@@ -4356,7 +5662,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）・フレームレート制御（</t>
     </r>
@@ -4376,12 +5681,54 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">src/tetris_cli/battle.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">お邪魔行の攻撃力算出・保留キュー管理・相殺・盤面反映・勝敗判定</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">src/tetris_cli/ui_curses.py</t>
   </si>
   <si>
@@ -4401,7 +5748,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">描画・キー入力。盤面</t>
     </r>
@@ -4421,9 +5767,46 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">サイドバー描画、配色、点滅エフェクト表示</t>
+      </rPr>
+      <t xml:space="preserve">サイドバー描画、配色、点滅エフェクト表示、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦の画面分割・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレイヤー入力</t>
     </r>
   </si>
   <si>
@@ -4449,7 +5832,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行ログを </t>
     </r>
@@ -4469,7 +5851,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ出力する仕組み（</t>
     </r>
@@ -4489,7 +5870,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）</t>
     </r>
@@ -4505,7 +5885,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">設計方針（</t>
     </r>
@@ -4527,7 +5906,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章）</t>
     </r>
@@ -4549,7 +5927,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">以下のロジック層は </t>
     </r>
@@ -4571,7 +5948,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を一切</t>
     </r>
@@ -4593,7 +5969,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">しない。</t>
     </r>
@@ -4615,7 +5990,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は </t>
     </r>
@@ -4637,7 +6011,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に閉じ込め、</t>
     </r>
@@ -4659,7 +6032,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の公開メソッドを呼び出すだけにすることで、</t>
     </r>
@@ -4681,7 +6053,6 @@
         <color rgb="FF6B7280"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">からロジックのみを直接テストできるようにしている。</t>
     </r>
@@ -4694,7 +6065,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">改訂履歴 — </t>
     </r>
@@ -4716,7 +6086,6 @@
         <color rgb="FF1F2A37"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">章</t>
     </r>
@@ -4734,7 +6103,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">初版作成。</t>
     </r>
@@ -4754,7 +6122,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4774,7 +6141,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4794,7 +6160,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -4814,7 +6179,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を定義。</t>
     </r>
@@ -4836,7 +6200,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -4856,7 +6219,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">環境で</t>
     </r>
@@ -4876,7 +6238,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">操作ヘルプ等の全角文字がずれて重なって表示される不具合が発見されたため、</t>
     </r>
@@ -4896,7 +6257,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">描画文字列を</t>
     </r>
@@ -4916,7 +6276,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">限定とする方針を明文化し、</t>
     </r>
@@ -4936,7 +6295,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を修正。</t>
     </r>
@@ -4958,7 +6316,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -4978,7 +6335,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">実行のたびに </t>
     </r>
@@ -4998,7 +6354,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ</t>
     </r>
@@ -5018,7 +6373,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ファイルの実行ログを残す要件を明文化し、</t>
     </r>
@@ -5038,7 +6392,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加して実装。</t>
     </r>
@@ -5060,7 +6413,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5080,7 +6432,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5100,7 +6451,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。ゲームループを「入力→固定タイムステップ更新→描画→フレームレート制御」に明確に分離するため、</t>
     </r>
@@ -5120,7 +6470,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（</t>
     </r>
@@ -5140,7 +6489,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）を新規実装し、</t>
     </r>
@@ -5160,7 +6508,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の </t>
     </r>
@@ -5180,7 +6527,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を書き換えた。壁打ちログ</t>
     </r>
@@ -5215,7 +6561,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5235,7 +6580,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。盤面のブロック（落下中ピース・固定ブロック）をミノの種類ごとに色分け表示するようにした。色非対応端末ではモノクロにフォールバックする。壁打ちログ</t>
     </r>
@@ -5267,7 +6611,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -5287,7 +6630,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更時に設計判断の壁打ち要旨を </t>
     </r>
@@ -5307,7 +6649,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">へ残す運用を明文化。</t>
     </r>
@@ -5327,7 +6668,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">、</t>
     </r>
@@ -5347,7 +6687,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（</t>
     </r>
@@ -5367,7 +6706,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）を新設。壁打ちログ</t>
     </r>
@@ -5399,7 +6737,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を改訂。</t>
     </r>
@@ -5419,7 +6756,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">画面の表示文字列を </t>
     </r>
@@ -5439,7 +6775,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">限定から日本語表示へ変更。</t>
     </r>
@@ -5459,7 +6794,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の全角文字重なり不具合は、表示幅を </t>
     </r>
@@ -5479,7 +6813,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">で明示計算して</t>
     </r>
@@ -5499,7 +6832,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">文字ずつ描画する方式で回避する。</t>
     </r>
@@ -5519,7 +6851,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に </t>
     </r>
@@ -5539,7 +6870,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加して実装。壁打ちログ</t>
     </r>
@@ -5571,7 +6901,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5591,7 +6920,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5611,7 +6939,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。盤面のブロックを輪郭表示から塗りつぶし表示に変更し、盤面の枠線・サイドバーのタイトル・一時停止</t>
     </r>
@@ -5631,7 +6958,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ゲームオーバーの状態メッセージに標準</t>
     </r>
@@ -5651,7 +6977,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">色でアクセントカラーを付けた（配色・見た目のモダン化）。色非対応端末では従来通りの無配色表示にフォールバックする。壁打ちログ</t>
     </r>
@@ -5683,7 +7008,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5703,7 +7027,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・</t>
     </r>
@@ -5723,7 +7046,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。横一列が完成してから実際に盤面から消去されるまでの間、対象行を一定時間・点滅（反転表示）させるライン消去エフェクトを追加した。エフェクト表示中は重力・新規ミノ出現・プレイヤー操作を一時停止する。壁打ちログ</t>
     </r>
@@ -5755,7 +7077,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。</t>
     </r>
@@ -5775,7 +7096,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の</t>
     </r>
@@ -5795,7 +7115,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">変更時に、</t>
     </r>
@@ -5815,7 +7134,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">配下の説明資料</t>
     </r>
@@ -5835,7 +7153,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">概要資料</t>
     </r>
@@ -5855,7 +7172,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・設計書</t>
     </r>
@@ -5875,7 +7191,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・要件一覧</t>
     </r>
@@ -5895,7 +7210,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">も更新することを明文化した。壁打ちログ</t>
     </r>
@@ -5927,7 +7241,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を追加。テストを新規作成・変更した場合、</t>
     </r>
@@ -5947,7 +7260,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">合格確認の後に、評価者</t>
     </r>
@@ -5967,7 +7279,6 @@
         <color rgb="FF222222"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">によるテスト観点レビューを別セッションで実行することを明文化した。壁打ちログ</t>
     </r>
@@ -5980,6 +7291,227 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: docs/spec-log/2026-09-12-reviewer-separate-session.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR-17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FR-22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NFR-16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC-19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を追加。同一端末・同一プロセスで画面分割する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人対戦モードを新設し、ライン消去数に応じた非線形の「お邪魔行」攻撃・相殺・遅延反映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手の次のミノロック時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・勝敗判定を仕様化・実装した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(battle.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新設</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。壁打ちログ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF222222"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/spec-log/2026-09-12-two-player-battle-mode.md</t>
     </r>
   </si>
 </sst>
@@ -6028,7 +7560,6 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -6042,7 +7573,6 @@
       <color rgb="FF4B5563"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -6050,14 +7580,12 @@
       <color rgb="FF3B6EA5"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -6072,7 +7600,6 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -6096,7 +7623,6 @@
       <color rgb="FF6B7280"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -6112,7 +7638,6 @@
       <color rgb="FF1F2A37"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -6136,14 +7661,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -6222,100 +7745,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6643,143 +8162,143 @@
   <dimension ref="B2:C24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <f aca="false">COUNTA('機能要件(FR)'!A3:A100)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <f aca="false">COUNTA('非機能要件(NFR)'!A3:A100)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <f aca="false">COUNTA('非機能要件(NFR)'!A3:A100)</f>
-        <v>13</v>
-      </c>
-    </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <f aca="false">COUNTA('受け入れ基準(AC)'!A3:A100)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="9" t="n">
-        <f aca="false">COUNTA(モジュール構成!A3:A9)</f>
-        <v>7</v>
+      <c r="C22" s="8" t="n">
+        <f aca="false">COUNTA(モジュール構成!A3:A10)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6806,301 +8325,397 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="15"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="18"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="18"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="17" t="s">
         <v>89</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="17"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E18"/>
+  <autoFilter ref="A2:E24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -7120,250 +8735,299 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="A3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="15"/>
+      <c r="D3" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="17"/>
+    </row>
+    <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="E16" s="18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="16" t="s">
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>133</v>
+      <c r="E18" s="18" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E15"/>
+  <autoFilter ref="A2:E18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -7383,221 +9047,305 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>136</v>
+      <c r="C2" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>116</v>
+      <c r="A13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>162</v>
+      <c r="B14" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>165</v>
+      <c r="B15" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D15"/>
+  <autoFilter ref="A2:D21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -7617,148 +9365,162 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="A2" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="19" t="s">
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="16" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>176</v>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>231</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D9"/>
+  <autoFilter ref="A2:D10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7776,117 +9538,125 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="108"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="108"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="11"/>
+      <c r="A1" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>195</v>
+      <c r="A3" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>196</v>
+      <c r="A4" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>197</v>
+      <c r="A5" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>198</v>
+      <c r="A6" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>200</v>
+      <c r="A7" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>201</v>
+      <c r="A8" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>202</v>
+      <c r="A9" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>203</v>
+      <c r="A10" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>204</v>
+      <c r="A11" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>205</v>
+      <c r="A12" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>206</v>
+      <c r="A13" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B13"/>
+  <autoFilter ref="A2:B14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
